--- a/Reports/DS1-Loan_Default.xlsx
+++ b/Reports/DS1-Loan_Default.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\PyCharm Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\PyCharmMiscProject\COMP3608 Project\COMP3608-LOANS-PROJECT\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349B89CC-C88D-481B-9A0B-CDA0262D1848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA6765B-7811-4E08-A775-71E5CE0D702C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A4A8BD8D-39C5-4DF3-9E3A-19A9A46E0113}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="145">
   <si>
     <t>Variable Name</t>
   </si>
@@ -172,30 +172,12 @@
     <t>Drop the observation with missing values</t>
   </si>
   <si>
-    <t>Keep</t>
-  </si>
-  <si>
-    <t>Impute</t>
-  </si>
-  <si>
     <t>Impute the value (sci-kit has imputer)</t>
   </si>
   <si>
     <t>Handle Missing Values</t>
   </si>
   <si>
-    <t>Drop column (no influence on default)</t>
-  </si>
-  <si>
-    <t>Drop column (no variability)</t>
-  </si>
-  <si>
-    <t>Consider dropping because of low variability</t>
-  </si>
-  <si>
-    <t>Not really useful</t>
-  </si>
-  <si>
     <t>How was the application submitted? To_inst =&gt; directly, not_inst =&gt; through a 3rd party</t>
   </si>
   <si>
@@ -220,18 +202,9 @@
     <t>Loan to value ratio-How much of the property’s value is being financed by the loan. A lower LTV represents lower risk since borrower uses more of their own money</t>
   </si>
   <si>
-    <t>Drop observations (true values are needed for modelling and therefore cannot be imputed)</t>
-  </si>
-  <si>
     <t>Debt to Income ratio-How much of a borrower’s income goes toward paying debts. A high DTI Ratio makes the loan harder to repay</t>
   </si>
   <si>
-    <t>Retain for reference but do not include when training the model (will confuse the model)</t>
-  </si>
-  <si>
-    <t>Drop column (low variance feature-zero variance provides no discriminative power)</t>
-  </si>
-  <si>
     <t>Pre-Cleaning Exploration: number of options, prop of missing values, rel frequency, variables, descriptions, correlation with target vars</t>
   </si>
   <si>
@@ -274,36 +247,18 @@
     <t>Num: Correlation</t>
   </si>
   <si>
-    <t>Cat: Grouped Averages</t>
-  </si>
-  <si>
     <t>Has Missing Values?</t>
   </si>
   <si>
-    <t>Num: Outliers present?</t>
-  </si>
-  <si>
     <t>Num: Min</t>
   </si>
   <si>
     <t>Num: Max</t>
   </si>
   <si>
-    <t>Drop Rows Criteria: missingess &lt; 5% ^ variable not critical</t>
-  </si>
-  <si>
-    <t>If we do not drop rows, then we impute</t>
-  </si>
-  <si>
     <t>Drop Column Criteria: missingness&gt;40%^variable not critical, top category frequency(%) &gt; 95%, SD=0, variable not useful</t>
   </si>
   <si>
-    <t>If variable is not too important then use simple imputation</t>
-  </si>
-  <si>
-    <t>If variable is important then use advanced imputation, use missing indicators</t>
-  </si>
-  <si>
     <t>int64</t>
   </si>
   <si>
@@ -418,10 +373,6 @@
     <t>45.0, 46.0, 42.0, 39.0, 40.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Cleaning Actions Being Considered
-</t>
-  </si>
-  <si>
     <t>No. Unique Values</t>
   </si>
   <si>
@@ -435,6 +386,90 @@
   </si>
   <si>
     <t>Correlation with Status</t>
+  </si>
+  <si>
+    <t>Drop vs Impute</t>
+  </si>
+  <si>
+    <t>Missingness &lt; 5%</t>
+  </si>
+  <si>
+    <t>Simple Imputaton: median for numeric, mode for categorical</t>
+  </si>
+  <si>
+    <t>Missingness between 5 and 30%</t>
+  </si>
+  <si>
+    <t>Simple Imputation and consider adding Missing Indicator</t>
+  </si>
+  <si>
+    <t>Missingness &gt; 30% and Variable not at all important</t>
+  </si>
+  <si>
+    <t>Drop rows</t>
+  </si>
+  <si>
+    <t>Missingness &gt; 30% and Variable is important</t>
+  </si>
+  <si>
+    <t>If model performs badly then you can consider advanced imputation after as something to try</t>
+  </si>
+  <si>
+    <t>Cleaning Actions</t>
+  </si>
+  <si>
+    <t>Drop Column</t>
+  </si>
+  <si>
+    <t>Add Missing Indicator?</t>
+  </si>
+  <si>
+    <t>Encode/Scaling</t>
+  </si>
+  <si>
+    <t>Yes: ID numbers have no predictive ability and will confuse the model</t>
+  </si>
+  <si>
+    <t>Dropped</t>
+  </si>
+  <si>
+    <t>Categorical-Nominal</t>
+  </si>
+  <si>
+    <t>Yes: no variability =&gt; no discriminative power</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Nominal-OHE</t>
+  </si>
+  <si>
+    <t>Numeric-Scale</t>
+  </si>
+  <si>
+    <t>Yes. Removed due to close to perfect performance</t>
+  </si>
+  <si>
+    <t>Yes: results in close to perfect performance</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Yes: low variability</t>
+  </si>
+  <si>
+    <t>Categorical-Ordinal</t>
+  </si>
+  <si>
+    <t>Ordinal-OrdinalEncoding</t>
+  </si>
+  <si>
+    <t>No: same as missing indicator for property value</t>
+  </si>
+  <si>
+    <t>Target</t>
   </si>
 </sst>
 </file>
@@ -759,12 +794,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -881,21 +916,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -904,35 +924,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -983,38 +974,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1394,1439 +1364,1542 @@
   <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="5" max="7" width="11.81640625" customWidth="1"/>
-    <col min="10" max="14" width="11.6328125" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" customWidth="1"/>
+    <col min="16" max="16" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8" t="s">
+      <c r="N2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>148670</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3">
+        <v>42917.476597535417</v>
+      </c>
+      <c r="K3" s="3">
+        <v>24890</v>
+      </c>
+      <c r="L3" s="3">
+        <v>173559</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1.703121969355285E-3</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2019</v>
+      </c>
+      <c r="L4" s="3">
+        <v>2019</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2.2492769220421072</v>
+      </c>
+      <c r="I5" s="3">
+        <v>93.134057223070883</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>28.483217865070291</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.61074863792291656</v>
+      </c>
+      <c r="I7" s="3">
+        <v>84.339004615530371</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>76.123629515033301</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="3">
+        <v>9.0132508239725573E-2</v>
+      </c>
+      <c r="I9" s="3">
+        <v>37.656864329186192</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>95.744938454294754</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>99.626017353870992</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>86.03484226811058</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="3">
+        <v>211</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>183909.31012708551</v>
+      </c>
+      <c r="K13" s="3">
+        <v>16500</v>
+      </c>
+      <c r="L13" s="3">
+        <v>3576500</v>
+      </c>
+      <c r="M13" s="3">
+        <v>-3.6825275544373967E-2</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="5"/>
-    </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="D14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="3">
+        <v>131</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" s="3">
+        <v>24.50998856527881</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>0.56139119346704236</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2.295707332398849E-2</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="3">
+        <v>22516</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="3">
+        <v>24.64451469697989</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>0.51304273578472881</v>
+      </c>
+      <c r="K15" s="3">
+        <v>-3.6379999999999999</v>
+      </c>
+      <c r="L15" s="3">
+        <v>3.3570000000000002</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="3">
+        <v>58271</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="3">
+        <v>26.664424564471648</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3">
+        <v>3251.1215097103259</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>60000</v>
+      </c>
+      <c r="M16" s="3">
+        <v>-1.913794191908548E-2</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="3">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2.7577856998721999E-2</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3">
+        <v>58.409083508964343</v>
+      </c>
+      <c r="K17" s="3">
+        <v>96</v>
+      </c>
+      <c r="L17" s="3">
+        <v>360</v>
+      </c>
+      <c r="M17" s="3">
+        <v>-2.3982428649335701E-4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18" s="3">
+        <v>8.1388309679155169E-2</v>
+      </c>
+      <c r="I18" s="3">
+        <v>89.815481760227271</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>95.217596018026512</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>97.723817851617682</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="3">
+        <v>385</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" s="3">
+        <v>10.15537768211475</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3">
+        <v>359935.31556194392</v>
+      </c>
+      <c r="K21" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>16508000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-4.886412718512826E-2</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>99.97780318826932</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>92.958229636106822</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>99.97780318826932</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>98.526938857873134</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1001</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="3">
+        <v>6.1545705253245444</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3">
+        <v>6496.5863822202537</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>578580</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-6.5118969608288974E-2</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>32.388511468352718</v>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="3">
+        <v>401</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3">
+        <v>115.87585660446859</v>
+      </c>
+      <c r="K28" s="3">
+        <v>500</v>
+      </c>
+      <c r="L28" s="3">
+        <v>900</v>
+      </c>
+      <c r="M28" s="3">
+        <v>4.0036935955881266E-3</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>50.038339947534801</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="3">
+        <v>7</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.13452613170108291</v>
+      </c>
+      <c r="I30" s="3">
+        <v>23.385195662423381</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.13452613170108291</v>
+      </c>
+      <c r="I31" s="3">
+        <v>64.534249343301681</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8484</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="3">
+        <v>10.15537768211475</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3">
+        <v>39.967602983032251</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0.96747819800000001</v>
+      </c>
+      <c r="L32" s="3">
+        <v>7831.25</v>
+      </c>
+      <c r="M32" s="3">
+        <v>3.8895466172237873E-2</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>50.260308064841603</v>
+      </c>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>99.97780318826932</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3">
+        <v>0.43094220686213142</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" s="10" t="s">
+      <c r="M35" s="3">
+        <v>1</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4">
-        <v>148670</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="11" t="str">
-        <f>IF(H3&gt;0,"Yes","No")</f>
-        <v>No</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4">
-        <v>42917.476597535417</v>
-      </c>
-      <c r="L3" s="4">
-        <v>24890</v>
-      </c>
-      <c r="M3" s="4">
-        <v>173559</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1.703121969355285E-3</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="11" t="str">
-        <f t="shared" ref="G4:G36" si="0">IF(H4&gt;0,"Yes","No")</f>
-        <v>No</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>2019</v>
-      </c>
-      <c r="M4" s="4">
-        <v>2019</v>
-      </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="E36" s="3">
+        <v>57</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36" s="3">
+        <v>16.22452411380911</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3">
+        <v>10.54543492987368</v>
+      </c>
+      <c r="K36" s="3">
         <v>5</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H5" s="4">
-        <v>2.2492769220421072</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4">
-        <v>93.134057223070883</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4">
-        <v>4</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4">
-        <v>28.483217865070291</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0.61074863792291656</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4">
-        <v>84.339004615530371</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4">
-        <v>76.123629515033301</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H9" s="4">
-        <v>9.0132508239725573E-2</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4">
-        <v>37.656864329186192</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4">
-        <v>95.744938454294754</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4">
-        <v>2</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4">
-        <v>99.626017353870992</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="4">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4">
-        <v>86.03484226811058</v>
-      </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="4">
-        <v>211</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4">
-        <v>183909.31012708551</v>
-      </c>
-      <c r="L13" s="4">
-        <v>16500</v>
-      </c>
-      <c r="M13" s="4">
-        <v>3576500</v>
-      </c>
-      <c r="N13" s="4">
-        <v>-3.6825275544373967E-2</v>
-      </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="4">
-        <v>131</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H14" s="4">
-        <v>24.50998856527881</v>
-      </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4">
-        <v>0.56139119346704236</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>8</v>
-      </c>
-      <c r="N14" s="4">
-        <v>2.295707332398849E-2</v>
-      </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="4">
-        <v>22516</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H15" s="4">
-        <v>24.64451469697989</v>
-      </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4">
-        <v>0.51304273578472881</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-3.6379999999999999</v>
-      </c>
-      <c r="M15" s="4">
-        <v>3.3570000000000002</v>
-      </c>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="4">
-        <v>58271</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H16" s="4">
-        <v>26.664424564471648</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4">
-        <v>3251.1215097103259</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
-        <v>60000</v>
-      </c>
-      <c r="N16" s="4">
-        <v>-1.913794191908548E-2</v>
-      </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="4">
-        <v>26</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H17" s="4">
-        <v>2.7577856998721999E-2</v>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4">
-        <v>58.409083508964343</v>
-      </c>
-      <c r="L17" s="4">
-        <v>96</v>
-      </c>
-      <c r="M17" s="4">
-        <v>360</v>
-      </c>
-      <c r="N17" s="4">
-        <v>-2.3982428649335701E-4</v>
-      </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="4">
-        <v>2</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H18" s="4">
-        <v>8.1388309679155169E-2</v>
-      </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4">
-        <v>89.815481760227271</v>
-      </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="4">
-        <v>2</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H19" s="4">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4">
-        <v>95.217596018026512</v>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="4">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H20" s="4">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4">
-        <v>97.723817851617682</v>
-      </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="4">
-        <v>385</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H21" s="4">
-        <v>10.15537768211475</v>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4">
-        <v>359935.31556194392</v>
-      </c>
-      <c r="L21" s="4">
-        <v>8000</v>
-      </c>
-      <c r="M21" s="4">
-        <v>16508000</v>
-      </c>
-      <c r="N21" s="4">
-        <v>-4.886412718512826E-2</v>
-      </c>
-      <c r="O21" s="4"/>
-      <c r="P21" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H22" s="4">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4">
-        <v>99.97780318826932</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="4">
-        <v>3</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H23" s="4">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4">
-        <v>92.958229636106822</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="4">
-        <v>2</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H24" s="4">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4">
-        <v>99.97780318826932</v>
-      </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="4">
-        <v>4</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G25" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H25" s="4">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4">
-        <v>98.526938857873134</v>
-      </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="4">
-        <v>1001</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H26" s="4">
-        <v>6.1545705253245444</v>
-      </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4">
-        <v>6496.5863822202537</v>
-      </c>
-      <c r="L26" s="4">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4">
-        <v>578580</v>
-      </c>
-      <c r="N26" s="4">
-        <v>-6.5118969608288974E-2</v>
-      </c>
-      <c r="O26" s="4"/>
-      <c r="P26" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="4">
-        <v>4</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G27" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H27" s="4">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4">
-        <v>32.388511468352718</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="4">
-        <v>401</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G28" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H28" s="4">
-        <v>0</v>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4">
-        <v>115.87585660446859</v>
-      </c>
-      <c r="L28" s="4">
-        <v>500</v>
-      </c>
-      <c r="M28" s="4">
-        <v>900</v>
-      </c>
-      <c r="N28" s="4">
-        <v>4.0036935955881266E-3</v>
-      </c>
-      <c r="O28" s="4"/>
-      <c r="P28" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="4">
-        <v>2</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G29" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H29" s="4">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4">
-        <v>50.038339947534801</v>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="4">
-        <v>7</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H30" s="4">
-        <v>0.13452613170108291</v>
-      </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4">
-        <v>23.385195662423381</v>
-      </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="4">
-        <v>2</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H31" s="4">
-        <v>0.13452613170108291</v>
-      </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4">
-        <v>64.534249343301681</v>
-      </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="4">
-        <v>8484</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H32" s="4">
-        <v>10.15537768211475</v>
-      </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4">
-        <v>39.967602983032251</v>
-      </c>
-      <c r="L32" s="4">
-        <v>0.96747819800000001</v>
-      </c>
-      <c r="M32" s="4">
-        <v>7831.25</v>
-      </c>
-      <c r="N32" s="4">
-        <v>3.8895466172237873E-2</v>
-      </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="4">
-        <v>4</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H33" s="4">
-        <v>0</v>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4">
-        <v>50.260308064841603</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="4">
-        <v>2</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G34" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H34" s="4">
-        <v>0</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4">
-        <v>99.97780318826932</v>
-      </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="4">
-        <v>2</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G35" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="H35" s="4">
-        <v>0</v>
-      </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4">
-        <v>0.43094220686213142</v>
-      </c>
-      <c r="L35" s="4">
-        <v>0</v>
-      </c>
-      <c r="M35" s="4">
-        <v>1</v>
-      </c>
-      <c r="N35" s="4">
-        <v>1</v>
-      </c>
-      <c r="O35" s="4"/>
-      <c r="P35" s="2" t="s">
+      <c r="L36" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" s="4">
-        <v>57</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G36" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="H36" s="4">
-        <v>16.22452411380911</v>
-      </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4">
-        <v>10.54543492987368</v>
-      </c>
-      <c r="L36" s="4">
-        <v>5</v>
-      </c>
-      <c r="M36" s="4">
-        <v>61</v>
-      </c>
-      <c r="N36" s="4">
+      <c r="M36" s="3">
         <v>7.8083066052822739E-2</v>
       </c>
-      <c r="O36" s="4"/>
-      <c r="P36" s="2" t="s">
-        <v>46</v>
+      <c r="N36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="E1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2834,12 +2907,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60FE4F7B-FA83-409D-94F8-D372F0C53166}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2857,72 +2930,117 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>57</v>
+      <c r="B8" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>66</v>
+      <c r="B10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>59</v>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>86</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
-        <v>88</v>
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2940,31 +3058,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" t="s">
-        <v>83</v>
-      </c>
       <c r="J1" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2972,13 +3090,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>148670</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3001,13 +3119,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3027,13 +3145,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E4">
         <v>2.2492769220421072</v>
@@ -3047,13 +3165,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3067,13 +3185,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E6">
         <v>0.61074863792291656</v>
@@ -3087,13 +3205,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3107,13 +3225,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>9.0132508239725573E-2</v>
@@ -3127,13 +3245,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -3147,13 +3265,13 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3167,13 +3285,13 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -3187,13 +3305,13 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C12">
         <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -3216,13 +3334,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C13">
         <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E13">
         <v>24.50998856527881</v>
@@ -3245,13 +3363,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <v>22516</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E14">
         <v>24.64451469697989</v>
@@ -3271,13 +3389,13 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>58271</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>26.664424564471648</v>
@@ -3300,13 +3418,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E16">
         <v>2.7577856998721999E-2</v>
@@ -3329,13 +3447,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E17">
         <v>8.1388309679155169E-2</v>
@@ -3349,13 +3467,13 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3369,13 +3487,13 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3389,13 +3507,13 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>385</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E20">
         <v>10.15537768211475</v>
@@ -3418,13 +3536,13 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -3438,13 +3556,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3458,13 +3576,13 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3478,13 +3596,13 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C24">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -3498,13 +3616,13 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C25">
         <v>1001</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E25">
         <v>6.1545705253245444</v>
@@ -3527,13 +3645,13 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -3547,13 +3665,13 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C27">
         <v>401</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3576,13 +3694,13 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -3596,13 +3714,13 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C29">
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E29">
         <v>0.13452613170108291</v>
@@ -3616,13 +3734,13 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E30">
         <v>0.13452613170108291</v>
@@ -3636,13 +3754,13 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C31">
         <v>8484</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E31">
         <v>10.15537768211475</v>
@@ -3665,13 +3783,13 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C32">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3685,13 +3803,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3705,13 +3823,13 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3734,13 +3852,13 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C35">
         <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E35">
         <v>16.22452411380911</v>
